--- a/upcoming_exhibitions_embeddings.xlsx
+++ b/upcoming_exhibitions_embeddings.xlsx
@@ -3263,7 +3263,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>72387</v>
+        <v>32646</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2012</v>
+        <v>1995</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
